--- a/artfynd/A 23588-2025 artfynd.xlsx
+++ b/artfynd/A 23588-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1529,6 +1529,108 @@
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>126421048</v>
+      </c>
+      <c r="B9" t="n">
+        <v>57656</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Brantbergtjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>556573</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6972681</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 23588-2025 artfynd.xlsx
+++ b/artfynd/A 23588-2025 artfynd.xlsx
@@ -1534,7 +1534,7 @@
         <v>126421048</v>
       </c>
       <c r="B9" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 23588-2025 artfynd.xlsx
+++ b/artfynd/A 23588-2025 artfynd.xlsx
@@ -1534,7 +1534,7 @@
         <v>126421048</v>
       </c>
       <c r="B9" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 23588-2025 artfynd.xlsx
+++ b/artfynd/A 23588-2025 artfynd.xlsx
@@ -1534,7 +1534,7 @@
         <v>126421048</v>
       </c>
       <c r="B9" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 23588-2025 artfynd.xlsx
+++ b/artfynd/A 23588-2025 artfynd.xlsx
@@ -1534,7 +1534,7 @@
         <v>126421048</v>
       </c>
       <c r="B9" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 23588-2025 artfynd.xlsx
+++ b/artfynd/A 23588-2025 artfynd.xlsx
@@ -1534,7 +1534,7 @@
         <v>126421048</v>
       </c>
       <c r="B9" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
